--- a/out/Attention-mamba2_repeat_4_000001.xlsx
+++ b/out/Attention-mamba2_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002308914800479542</v>
+        <v>-7.549743061384651e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.0994151676256133</v>
+        <v>0.03250700163653785</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1990956480491059</v>
+        <v>0.06510075586587261</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3840933685733444</v>
+        <v>0.1255909113784595</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8681214476066218</v>
+        <v>0.2838603620831945</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1181487642780713</v>
+        <v>0.03863297737825833</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7198403969586303</v>
+        <v>0.2353747611161221</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02397346970373226</v>
+        <v>0.00783871192263551</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6494527200054233</v>
+        <v>0.2123591837899089</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02076173242546269</v>
+        <v>0.006787130236714228</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6669769286468106</v>
+        <v>0.2180879121040965</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01014993978804303</v>
+        <v>0.003315884100197597</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6664882790969077</v>
+        <v>0.217924827968996</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00484191686697163</v>
+        <v>0.001579903061546279</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6660105425956556</v>
+        <v>0.2177652469128931</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002014187906428512</v>
+        <v>0.0006552583008062353</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6651914368603129</v>
+        <v>0.2174940408466905</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001394040411417359</v>
+        <v>0.0004526011935854903</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6659642739381986</v>
+        <v>0.217743387102616</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005793683304635861</v>
+        <v>0.0001857089590046543</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6657266768262635</v>
+        <v>0.2176623513565788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002976817398315617</v>
+        <v>9.388939844386562e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6657427318276949</v>
+        <v>0.2176642463538488</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001141441476242028</v>
+        <v>3.383994239731721e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6656723132541699</v>
+        <v>0.2176377769955543</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.970755853095545e-05</v>
+        <v>1.618743066942789e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6656780246188224</v>
+        <v>0.2176363164230874</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.718628873473194e-05</v>
+        <v>5.728762911577315e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.665672043183505</v>
+        <v>0.2176309892779815</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>-2.045694596194254e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6656651911179956</v>
+        <v>0.2176253723353827</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-2.694140733653212e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6656580945395848</v>
+        <v>0.2176196491787541</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6656523694814483</v>
+        <v>0.2176144078574532</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6656466003385808</v>
+        <v>0.2176091199186027</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6656410566704783</v>
+        <v>0.2176038480845517</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6656361355167569</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6656361753722292</v>
+        <v>0.2176039277954963</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6656361674011347</v>
+        <v>0.2176039198244019</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6656363268230239</v>
+        <v>0.217604079246291</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6656365818980466</v>
+        <v>0.2176043343213138</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6656363347941183</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6656362949386461</v>
+        <v>0.2176040473619131</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6656363029097405</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6656363347941183</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.665636430447252</v>
+        <v>0.2176041828705191</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6656363666784961</v>
+        <v>0.2176041191017632</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6656363268230239</v>
+        <v>0.217604079246291</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6656363029097405</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6656360558058123</v>
+        <v>0.2176038082290795</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6656359760948676</v>
+        <v>0.2176037285181347</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6656360239214343</v>
+        <v>0.2176037763447014</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6656361434878514</v>
+        <v>0.2176038959111185</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6656361275456625</v>
+        <v>0.2176038799689296</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6656361434878514</v>
+        <v>0.2176038959111185</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6656361275456625</v>
+        <v>0.2176038799689296</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6656361833433236</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6656361833433236</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6656361833433236</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6656363347941183</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6656365500136688</v>
+        <v>0.217604302436936</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6656364623316299</v>
+        <v>0.2176042147548969</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6656364145050631</v>
+        <v>0.2176041669283302</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6656364623316299</v>
+        <v>0.2176042147548969</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6656362789964572</v>
+        <v>0.2176040314197242</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6656362869675516</v>
+        <v>0.2176040393908187</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6656362949386461</v>
+        <v>0.2176040473619131</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6656363029097405</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6656363029097405</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6656363427652128</v>
+        <v>0.2176040951884799</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6656364065339686</v>
+        <v>0.2176041589572358</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.665636518129291</v>
+        <v>0.2176042705525581</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6656365659558577</v>
+        <v>0.2176043183791249</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6656365261003855</v>
+        <v>0.2176042785236526</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6656364543605354</v>
+        <v>0.2176042067838025</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6656365739269522</v>
+        <v>0.2176043263502193</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6656364145050631</v>
+        <v>0.2176041669283302</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6656361833433236</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6656361355167569</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6656361674011347</v>
+        <v>0.2176039198244019</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6656361514589458</v>
+        <v>0.2176039038822129</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6656360318925287</v>
+        <v>0.2176037843157959</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6656359920370565</v>
+        <v>0.2176037444603236</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6656361355167569</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6656362710253626</v>
+        <v>0.2176040234486298</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6656362550831737</v>
+        <v>0.2176040075064408</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6656361913144181</v>
+        <v>0.2176039437376852</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6656360876901902</v>
+        <v>0.2176038401134573</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6656359681237731</v>
+        <v>0.2176037205470402</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6656360876901902</v>
+        <v>0.2176038401134573</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6656361355167569</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6656361116034736</v>
+        <v>0.2176038640267406</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.665636119574568</v>
+        <v>0.2176038719978351</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000001.xlsx
+++ b/out/Attention-mamba2_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.2301325296679071</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.8717978745164386</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679075</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.4301325296679073</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.204705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679073</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.204705233669807</v>
+        <v>0.4115328151806242</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.602580650042519</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.204705233669807</v>
+        <v>-0.2301325296679073</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.204705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679075</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.602580650042519</v>
+        <v>0.4115328151806242</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002308914800479542</v>
+        <v>-0.0001860202577076852</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.0994151676256133</v>
+        <v>0.08009492207309066</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1990956480491059</v>
+        <v>0.1604035963167874</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3840933685733444</v>
+        <v>0.3094490424290841</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8681214476066218</v>
+        <v>0.6994115823239512</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1181487642780713</v>
+        <v>0.09518826013331809</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.602580650042519</v>
+        <v>0.4115328151806243</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7198403969586303</v>
+        <v>0.5799473237868575</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02397346970373226</v>
+        <v>0.01931419948851758</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679073</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6494527200054233</v>
+        <v>0.5232389634947266</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02076173242546269</v>
+        <v>0.01672731292402344</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6669769286468106</v>
+        <v>0.5373576241610777</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01014993978804303</v>
+        <v>0.008176807201329997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6664882790969077</v>
+        <v>0.5369631453729128</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00484191686697163</v>
+        <v>0.003899794895310477</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6660105425956556</v>
+        <v>0.5365772972734757</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002014187906428512</v>
+        <v>0.001621707213284839</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6651914368603129</v>
+        <v>0.5359164337612971</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001394040411417359</v>
+        <v>0.001122412046928164</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679075</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6659642739381986</v>
+        <v>0.5365380777409042</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005793683304635861</v>
+        <v>0.000465329527274992</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.4301325296679073</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6657266768262635</v>
+        <v>0.5363457441485829</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002976817398315617</v>
+        <v>0.0002388826380541281</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.204705233669807</v>
+        <v>0.4115328151806243</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6657427318276949</v>
+        <v>0.5363577136406168</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001141441476242028</v>
+        <v>9.105012782039255e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.602580650042519</v>
+        <v>0.4115328151806243</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6656723132541699</v>
+        <v>0.5362999753192288</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.970755853095545e-05</v>
+        <v>4.710962678156589e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6656780246188224</v>
+        <v>0.5363036105968203</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.718628873473194e-05</v>
+        <v>2.097489968066087e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.665672043183505</v>
+        <v>0.5362978185613011</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>7.254989158750358e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6656651911179956</v>
+        <v>0.5362913234125147</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6656580945395848</v>
+        <v>0.5362846607280811</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.602580650042519</v>
+        <v>0.4115328151806243</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6656523694814483</v>
+        <v>0.5362790802438785</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.804705233669807</v>
+        <v>0.4115328151806243</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6656466003385808</v>
+        <v>0.5362735033867277</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.4301325296679073</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6656410566704783</v>
+        <v>0.5362680960440708</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.804705233669807</v>
+        <v>0.2115328151806243</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6656361355167569</v>
+        <v>0.5362631748903494</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.4301325296679073</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6656361753722292</v>
+        <v>0.5362632147458216</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679073</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6656361674011347</v>
+        <v>0.5362632067747272</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679073</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6656363268230239</v>
+        <v>0.5362633661966163</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.4301325296679072</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.5362632705434829</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679072</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6656365818980466</v>
+        <v>0.5362636212716392</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6656363347941183</v>
+        <v>0.5362633741677107</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679072</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6656362949386461</v>
+        <v>0.5362633343122385</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.002580650042519</v>
+        <v>0.2115328151806244</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.5362632705434829</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6656363029097405</v>
+        <v>0.5362633422833329</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.602580650042519</v>
+        <v>0.4115328151806245</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.5362632705434829</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.204705233669807</v>
+        <v>0.4115328151806244</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6656363347941183</v>
+        <v>0.5362633741677107</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.602580650042519</v>
+        <v>0.4115328151806244</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.665636430447252</v>
+        <v>0.5362634698208445</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6656363666784961</v>
+        <v>0.5362634060520886</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.602580650042519</v>
+        <v>0.4115328151806245</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6656363268230239</v>
+        <v>0.5362633661966163</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.204705233669807</v>
+        <v>0.4115328151806245</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6656363029097405</v>
+        <v>0.5362633422833329</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.002580650042519</v>
+        <v>0.2115328151806245</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6656360558058123</v>
+        <v>0.5362630951794048</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.002580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6656359760948676</v>
+        <v>0.53626301546846</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6656360239214343</v>
+        <v>0.5362630632950268</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6656361434878514</v>
+        <v>0.5362631828614438</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6656361275456625</v>
+        <v>0.5362631669192549</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6656361434878514</v>
+        <v>0.5362631828614438</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6656361275456625</v>
+        <v>0.5362631669192549</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6656361833433236</v>
+        <v>0.5362632227169161</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.602580650042519</v>
+        <v>0.2115328151806244</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6656361833433236</v>
+        <v>0.5362632227169161</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.804705233669807</v>
+        <v>0.2115328151806244</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6656361833433236</v>
+        <v>0.5362632227169161</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.002580650042519</v>
+        <v>0.2115328151806244</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6656363347941183</v>
+        <v>0.5362633741677107</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.002580650042519</v>
+        <v>0.8531981600291557</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6656365500136688</v>
+        <v>0.5362635893872613</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.602580650042519</v>
+        <v>0.8531981600291557</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6656364623316299</v>
+        <v>0.5362635017052223</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6656364145050631</v>
+        <v>0.5362634538786556</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6656364623316299</v>
+        <v>0.5362635017052223</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6656362789964572</v>
+        <v>0.5362633183700496</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6656362869675516</v>
+        <v>0.536263326341144</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6656362949386461</v>
+        <v>0.5362633343122385</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6656363029097405</v>
+        <v>0.5362633422833329</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.002580650042519</v>
+        <v>0.2115328151806244</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6656363029097405</v>
+        <v>0.5362633422833329</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.804705233669807</v>
+        <v>0.2115328151806244</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6656363427652128</v>
+        <v>0.5362633821388052</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.4301325296679072</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6656364065339686</v>
+        <v>0.5362634459075611</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.804705233669807</v>
+        <v>0.2115328151806245</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.665636518129291</v>
+        <v>0.5362635575028835</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.002580650042519</v>
+        <v>-0.430132529667907</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6656365659558577</v>
+        <v>0.5362636053294502</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.430132529667907</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6656365261003855</v>
+        <v>0.5362635654739779</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6656364543605354</v>
+        <v>0.5362634937341278</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.804705233669807</v>
+        <v>-1.071797874516439</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6656365739269522</v>
+        <v>0.5362636133005447</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.4301325296679072</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6656364145050631</v>
+        <v>0.5362634538786556</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.002580650042519</v>
+        <v>0.2115328151806245</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6656361833433236</v>
+        <v>0.5362632227169161</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6656361355167569</v>
+        <v>0.5362631748903494</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6656361674011347</v>
+        <v>0.5362632067747272</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.5362632705434829</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.5362632705434829</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6656361514589458</v>
+        <v>0.5362631908325383</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6656360318925287</v>
+        <v>0.5362630712661213</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6656359920370565</v>
+        <v>0.5362630314106489</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6656361355167569</v>
+        <v>0.5362631748903494</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.002580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6656362710253626</v>
+        <v>0.5362633103989551</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.002580650042519</v>
+        <v>0.8531981600291557</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6656362550831737</v>
+        <v>0.5362632944567662</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.002580650042519</v>
+        <v>0.8531981600291557</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.5362632705434829</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.002580650042519</v>
+        <v>0.2115328151806246</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6656361913144181</v>
+        <v>0.5362632306880106</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.430132529667907</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6656360876901902</v>
+        <v>0.5362631270637827</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.804705233669807</v>
+        <v>-0.430132529667907</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6656359681237731</v>
+        <v>0.5362630074973656</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.002580650042519</v>
+        <v>0.2115328151806245</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6656360876901902</v>
+        <v>0.5362631270637827</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.002580650042519</v>
+        <v>0.8531981600291557</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6656361355167569</v>
+        <v>0.5362631748903494</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6656362311698903</v>
+        <v>0.5362632705434829</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6656361116034736</v>
+        <v>0.536263150977066</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.602580650042519</v>
+        <v>1.053198160029156</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.665636119574568</v>
+        <v>0.5362631589481605</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000001.xlsx
+++ b/out/Attention-mamba2_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0569765716791153</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1281367987394333</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.08152145147323608</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.05962138995528221</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.06003609672188759</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.08888334035873413</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.07185764610767365</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.05854448303580284</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.07182779908180237</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.04854105412960052</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.06425344944000244</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0547046959400177</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.08238695561885834</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.09860144555568695</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.071797874516439</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.005205173045396805</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2301325296679071</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.03354078158736229</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2301325296679073</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.04256746917963028</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2301325296679073</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01131843402981758</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2301325296679073</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.006195083260536194</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.2301325296679073</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01762001216411591</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.2301325296679073</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.02393268793821335</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8717978745164386</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01948028057813644</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.071797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.01268459111452103</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4301325296679075</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0189957283437252</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4301325296679073</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.03183111548423767</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2301325296679073</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.01880207657814026</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.071797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.009661085903644562</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.071797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.007937503978610039</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.071797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.006473302841186523</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4301325296679073</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.05577022209763527</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.2301325296679073</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.03418011218309402</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4115328151806242</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.003926817327737808</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2301325296679073</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.01842448115348816</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2301325296679073</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.005615901201963425</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.071797874516439</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.007346823811531067</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.008938953280448914</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.071797874516439</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.011473149061203</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.071797874516439</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.003486255183815956</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4301325296679075</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.07318657636642456</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4115328151806242</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.05337734892964363</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.053198160029156</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.03958774730563164</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.053198160029156</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02565302699804306</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.053198160029156</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001860202577076852</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.08009492207309066</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01965414360165596</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.053198160029156</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1604035963167874</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3094490424290841</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01080069690942764</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6994115823239512</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.09518826013331809</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.008635006844997406</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4115328151806243</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.5799473237868575</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01931419948851758</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.00724560022354126</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4301325296679073</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.5232389634947266</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01672731292402344</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.02583774365484715</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5373576241610777</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008176807201329997</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.02329274825751781</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5369631453729128</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003899794895310477</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.02277077734470367</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5365772972734757</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001621707213284839</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.02719026990234852</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5359164337612971</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001122412046928164</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.008566072210669518</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4301325296679075</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5365380777409042</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000465329527274992</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.006030820310115814</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4301325296679073</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5363457441485829</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002388826380541281</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.02338235825300217</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4115328151806243</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5363577136406168</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>9.105012782039255e-05</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.003321614116430283</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4115328151806243</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5362999753192288</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.710962678156589e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.002590855583548546</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.053198160029156</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5363036105968203</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.097489968066087e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.04423921182751656</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.053198160029156</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5362978185613011</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.254989158750358e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01074445992708206</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.053198160029156</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5362913234125147</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>7.289038596293463e-08</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0100877545773983</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.053198160029156</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5362846607280811</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.519583929697793e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.008877705782651901</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.4115328151806243</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5362790802438785</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01931843347847462</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.4115328151806243</v>
+        <v>0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5362735033867277</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.009435482323169708</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4301325296679073</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5362680960440708</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.02711100503802299</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2115328151806243</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5362631748903494</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.03091924637556076</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4301325296679073</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5362632147458216</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.02441221289336681</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4301325296679073</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5362632067747272</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01087593659758568</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4301325296679073</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5362633661966163</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>-0.01245494931936264</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4301325296679072</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5362632705434829</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02327780984342098</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4301325296679072</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5362636212716392</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.007729392498731613</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5362633741677107</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0291189830750227</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4301325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5362633343122385</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.04884561523795128</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2115328151806244</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5362632705434829</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01096217334270477</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.053198160029156</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5362633422833329</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.02165169268846512</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4115328151806245</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5362632705434829</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.007592542096972466</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4115328151806244</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5362633741677107</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.04093126580119133</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4115328151806244</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5362634698208445</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.0507320873439312</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.053198160029156</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5362634060520886</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.02734263986349106</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.4115328151806245</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5362633661966163</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01898818090558052</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4115328151806245</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5362633422833329</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.04535405710339546</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2115328151806245</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5362630951794048</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.03726151958107948</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.53626301546846</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.02554597705602646</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5362630632950268</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02112023159861565</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5362631828614438</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01480599120259285</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5362631669192549</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01987652853131294</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5362631828614438</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01488315686583519</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.053198160029156</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5362631669192549</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.02968814596533775</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5362632227169161</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0140623040497303</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2115328151806244</v>
+        <v>-0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5362632227169161</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.002457642927765846</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2115328151806244</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5362632227169161</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.04664244130253792</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2115328151806244</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5362633741677107</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.006842717528343201</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8531981600291557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5362635893872613</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.07082806527614594</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8531981600291557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5362635017052223</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01359378546476364</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5362634538786556</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.002085287123918533</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5362635017052223</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.04393072053790092</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5362633183700496</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01854344829916954</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.536263326341144</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.02103626355528831</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5362633343122385</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.03011583909392357</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5362633422833329</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01104714721441269</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2115328151806244</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5362633422833329</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0137220798060298</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2115328151806244</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5362633821388052</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01037243381142616</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4301325296679072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5362634459075611</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.001807713881134987</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2115328151806245</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5362635575028835</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.03301410749554634</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.430132529667907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5362636053294502</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.000536968931555748</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.430132529667907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5362635654739779</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.0009352546185255051</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5362634937341278</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.005391914397478104</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.071797874516439</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5362636133005447</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02291898988187313</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4301325296679072</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5362634538786556</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.04922794178128242</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.2115328151806245</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5362632227169161</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.02745924517512321</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.053198160029156</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5362631748903494</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0263783372938633</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.053198160029156</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5362632067747272</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.01795312017202377</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.053198160029156</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5362632705434829</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.03258451819419861</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.053198160029156</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5362632705434829</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.02353865280747414</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.053198160029156</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5362631908325383</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0210895724594593</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.053198160029156</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5362630712661213</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.02048661932349205</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5362630314106489</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0171002559363842</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5362631748903494</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.03135119006037712</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.053198160029156</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5362633103989551</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.02483448758721352</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8531981600291557</v>
+        <v>-0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5362632944567662</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02130171656608582</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8531981600291557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5362632705434829</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01536605879664421</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2115328151806246</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5362632306880106</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01282423362135887</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.430132529667907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5362631270637827</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.03115666285157204</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.430132529667907</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5362630074973656</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.05475149676203728</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2115328151806245</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5362631270637827</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01464273408055305</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.8531981600291557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5362631748903494</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.03359007462859154</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.053198160029156</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5362632705434829</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01083404943346977</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.053198160029156</v>
+        <v>0.5099999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.536263150977066</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.02272163331508636</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.053198160029156</v>
+        <v>0.4399999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5362631589481605</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000001.xlsx
+++ b/out/Attention-mamba2_repeat_4_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.0569765716791153</v>
+        <v>-0.0560346394777298</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1281367987394333</v>
+        <v>-0.1252919435501099</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.08152145147323608</v>
+        <v>-0.07879172265529633</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.05962138995528221</v>
+        <v>-0.05717379599809647</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.06003609672188759</v>
+        <v>-0.05738568678498268</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.08888334035873413</v>
+        <v>-0.0851442813873291</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.07185764610767365</v>
+        <v>-0.06839635968208313</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.05854448303580284</v>
+        <v>-0.0546187236905098</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.07182779908180237</v>
+        <v>-0.06738820672035217</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.04854105412960052</v>
+        <v>-0.04483155906200409</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.06425344944000244</v>
+        <v>-0.05988214910030365</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0547046959400177</v>
+        <v>-0.05094411969184875</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.08238695561885834</v>
+        <v>-0.07871110737323761</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.09860144555568695</v>
+        <v>-0.09620128571987152</v>
       </c>
       <c r="JB15" t="n">
         <v>0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.005205173045396805</v>
+        <v>-0.004537679255008698</v>
       </c>
       <c r="JB16" t="n">
         <v>0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.03354078158736229</v>
+        <v>0.03337641805410385</v>
       </c>
       <c r="JB17" t="n">
         <v>0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.04256746917963028</v>
+        <v>-0.04200001806020737</v>
       </c>
       <c r="JB18" t="n">
         <v>0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.01131843402981758</v>
+        <v>-0.01006316021084785</v>
       </c>
       <c r="JB19" t="n">
         <v>0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.006195083260536194</v>
+        <v>0.007826924324035645</v>
       </c>
       <c r="JB20" t="n">
         <v>0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.01762001216411591</v>
+        <v>-0.01426904834806919</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.02393268793821335</v>
+        <v>-0.02033130452036858</v>
       </c>
       <c r="JB22" t="n">
         <v>0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.01948028057813644</v>
+        <v>-0.01801363006234169</v>
       </c>
       <c r="JB23" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.01268459111452103</v>
+        <v>-0.01171872764825821</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.02000000000000007</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0189957283437252</v>
+        <v>0.01991318911314011</v>
       </c>
       <c r="JB25" t="n">
         <v>0.1199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.03183111548423767</v>
+        <v>-0.03065290302038193</v>
       </c>
       <c r="JB26" t="n">
         <v>0.1199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.01880207657814026</v>
+        <v>-0.01720170117914677</v>
       </c>
       <c r="JB27" t="n">
         <v>0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.009661085903644562</v>
+        <v>-0.007988628000020981</v>
       </c>
       <c r="JB28" t="n">
         <v>0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.007937503978610039</v>
+        <v>-0.006486933678388596</v>
       </c>
       <c r="JB29" t="n">
         <v>0.8599999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.006473302841186523</v>
+        <v>-0.005331173539161682</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.05577022209763527</v>
+        <v>0.05624441802501678</v>
       </c>
       <c r="JB31" t="n">
         <v>0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.03418011218309402</v>
+        <v>-0.03352831304073334</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.02000000000000007</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.003926817327737808</v>
+        <v>0.005530744791030884</v>
       </c>
       <c r="JB33" t="n">
         <v>0.1199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.01842448115348816</v>
+        <v>-0.01720006391406059</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.005615901201963425</v>
+        <v>-0.004024164751172066</v>
       </c>
       <c r="JB35" t="n">
         <v>0.1199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.007346823811531067</v>
+        <v>-0.005826588720083237</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.02000000000000007</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.008938953280448914</v>
+        <v>-0.007332645356655121</v>
       </c>
       <c r="JB37" t="n">
         <v>0.1199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.011473149061203</v>
+        <v>-0.009918112307786942</v>
       </c>
       <c r="JB38" t="n">
         <v>0.1199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.003486255183815956</v>
+        <v>-0.002484537661075592</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.07318657636642456</v>
+        <v>0.07283935695886612</v>
       </c>
       <c r="JB40" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.05337734892964363</v>
+        <v>0.05205989629030228</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.03958774730563164</v>
+        <v>0.03843848407268524</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.02565302699804306</v>
+        <v>0.02437702938914299</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.01965414360165596</v>
+        <v>0.0183618925511837</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.01080069690942764</v>
+        <v>0.009461391717195511</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.008635006844997406</v>
+        <v>0.007284644991159439</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.00724560022354126</v>
+        <v>-0.006668899208307266</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.02583774365484715</v>
+        <v>-0.0309190321713686</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.02329274825751781</v>
+        <v>-0.0274931937456131</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.02277077734470367</v>
+        <v>-0.02745027095079422</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.02719026990234852</v>
+        <v>-0.0308798011392355</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.008566072210669518</v>
+        <v>-0.01187045872211456</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.7199999999999999</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.006030820310115814</v>
+        <v>0.01375780999660492</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0.4908470842272644</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.02338235825300217</v>
+        <v>-0.02406720444560051</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC54" t="n">
         <v>0.4908576145057606</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.003321614116430283</v>
+        <v>0.0003210306167602539</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0.4908043437054495</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.002590855583548546</v>
+        <v>0.0004484150558710098</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
         <v>0.4908072705833183</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.04423921182751656</v>
+        <v>0.04362146556377411</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0.4908015474204531</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.01074445992708206</v>
+        <v>0.009883064776659012</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0.4907951822846045</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0100877545773983</v>
+        <v>0.009075164794921875</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0.4907886642314969</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.008877705782651901</v>
+        <v>0.007596958428621292</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0.4907831326680945</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.01931843347847462</v>
+        <v>-0.02170408889651299</v>
       </c>
       <c r="JB61" t="n">
         <v>0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.009435482323169708</v>
+        <v>0.007667563855648041</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.3</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.02711100503802299</v>
+        <v>-0.03003194741904736</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.5799999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.03091924637556076</v>
+        <v>0.029599878937006</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.5799999999999998</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.02441221289336681</v>
+        <v>-0.0275376420468092</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0.4907672591989432</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.01087593659758568</v>
+        <v>-0.01402687001973391</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0.4907674186208323</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.01245494931936264</v>
+        <v>0.03543367981910706</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0.4907673229676988</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.02327780984342098</v>
+        <v>-0.0272626057267189</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0.4907676736958551</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.007729392498731613</v>
+        <v>-0.01055845804512501</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0.4907674265919267</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0291189830750227</v>
+        <v>-0.03229270130395889</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0.4907673867364544</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.04884561523795128</v>
+        <v>0.04797561466693878</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC71" t="n">
         <v>0.4907673229676988</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.01096217334270477</v>
+        <v>0.009914860129356384</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC72" t="n">
         <v>0.4907673947075489</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.02165169268846512</v>
+        <v>0.01987806707620621</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0.4907673229676988</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.007592542096972466</v>
+        <v>-0.008854812011122704</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0.4907674265919267</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.04093126580119133</v>
+        <v>0.03710152953863144</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.0507320873439312</v>
+        <v>0.04915948212146759</v>
       </c>
       <c r="JB76" t="n">
         <v>0.4399999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.02734263986349106</v>
+        <v>0.02629308775067329</v>
       </c>
       <c r="JB77" t="n">
         <v>0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.01898818090558052</v>
+        <v>-0.02178661897778511</v>
       </c>
       <c r="JB78" t="n">
         <v>0.5799999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.04535405710339546</v>
+        <v>0.04425694048404694</v>
       </c>
       <c r="JB79" t="n">
         <v>0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.03726151958107948</v>
+        <v>0.03638020157814026</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.02554597705602646</v>
+        <v>0.02493420615792274</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.02000000000000007</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.02112023159861565</v>
+        <v>0.02015168219804764</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.16</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.01480599120259285</v>
+        <v>0.01414455845952034</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.16</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.01987652853131294</v>
+        <v>0.01926422864198685</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.01488315686583519</v>
+        <v>0.01412090659141541</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.02968814596533775</v>
+        <v>0.0291135199368</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.0140623040497303</v>
+        <v>0.01251272484660149</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.002457642927765846</v>
+        <v>-0.005927052348852158</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.04664244130253792</v>
+        <v>0.04550948739051819</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.006842717528343201</v>
+        <v>0.004029069095849991</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.07082806527614594</v>
+        <v>0.07022546976804733</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.01359378546476364</v>
+        <v>0.01284929364919662</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.002085287123918533</v>
+        <v>0.0005751326680183411</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.04393072053790092</v>
+        <v>0.04330432415008545</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.01854344829916954</v>
+        <v>0.01794195547699928</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.02103626355528831</v>
+        <v>0.02046994119882584</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.03011583909392357</v>
+        <v>0.02943690493702888</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.01104714721441269</v>
+        <v>0.009680099785327911</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.5799999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.0137220798060298</v>
+        <v>-0.01628803089261055</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.01037243381142616</v>
+        <v>0.008550435304641724</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.001807713881134987</v>
+        <v>-0.003722604364156723</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.03301410749554634</v>
+        <v>0.03229385986924171</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.000536968931555748</v>
+        <v>-0.001900911331176758</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.0009352546185255051</v>
+        <v>-0.0006916746497154236</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.005391914397478104</v>
+        <v>-0.007723977789282799</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.02291898988187313</v>
+        <v>-0.02679966762661934</v>
       </c>
       <c r="JB106" t="n">
         <v>0.16</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.04922794178128242</v>
+        <v>0.04814024269580841</v>
       </c>
       <c r="JB107" t="n">
         <v>0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.02745924517512321</v>
+        <v>0.0267469733953476</v>
       </c>
       <c r="JB108" t="n">
         <v>0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.0263783372938633</v>
+        <v>0.02555583417415619</v>
       </c>
       <c r="JB109" t="n">
         <v>0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.01795312017202377</v>
+        <v>0.01725979149341583</v>
       </c>
       <c r="JB110" t="n">
         <v>0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.03258451819419861</v>
+        <v>0.03180387988686562</v>
       </c>
       <c r="JB111" t="n">
         <v>0.5799999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.02353865280747414</v>
+        <v>0.02267052605748177</v>
       </c>
       <c r="JB112" t="n">
         <v>0.4399999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.0210895724594593</v>
+        <v>0.02048657462000847</v>
       </c>
       <c r="JB113" t="n">
         <v>0.4399999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.02048661932349205</v>
+        <v>0.01967130973935127</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.0171002559363842</v>
+        <v>0.01647056639194489</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.03135119006037712</v>
+        <v>0.03083158284425735</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.02000000000000007</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.02483448758721352</v>
+        <v>0.02404271066188812</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.02130171656608582</v>
+        <v>0.02068489417433739</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.3</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.01536605879664421</v>
+        <v>0.01433957368135452</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.01282423362135887</v>
+        <v>-0.01497692335397005</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.03115666285157204</v>
+        <v>-0.03441009670495987</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.5799999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.05475149676203728</v>
+        <v>0.05409766733646393</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.01464273408055305</v>
+        <v>0.01366985589265823</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.03359007462859154</v>
+        <v>0.03290022909641266</v>
       </c>
       <c r="JB124" t="n">
         <v>0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.01083404943346977</v>
+        <v>0.009886655956506729</v>
       </c>
       <c r="JB125" t="n">
         <v>0.5099999999999998</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.02272163331508636</v>
+        <v>0.02032699435949326</v>
       </c>
       <c r="JB126" t="n">
         <v>0.4399999999999998</v>
